--- a/fcha_tantan_renewal/data/커피 자료.xlsx
+++ b/fcha_tantan_renewal/data/커피 자료.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\web\aix_web_1007\team01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\team\team-1\fcha_tantan_renewal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF745416-C863-4F0D-8B1F-038529762A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A614120-1B54-4B22-A4FF-AE8D4D6A90BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61AA3BB3-52B6-4F0F-ACA1-74F796FB93FC}"/>
+    <workbookView xWindow="1215" yWindow="-14160" windowWidth="21600" windowHeight="11295" xr2:uid="{61AA3BB3-52B6-4F0F-ACA1-74F796FB93FC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1534,6 +1537,156 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1543,172 +1696,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1724,9 +1727,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1764,7 +1767,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1870,7 +1873,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2012,7 +2015,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2023,7 +2026,9 @@
   <dimension ref="B1:AX131"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.125" customWidth="1"/>
+    <col min="7" max="7" width="14.25" customWidth="1"/>
     <col min="25" max="25" width="10.625" customWidth="1"/>
     <col min="26" max="26" width="7.5" bestFit="1" customWidth="1"/>
     <col min="27" max="29" width="9.375" bestFit="1" customWidth="1"/>
@@ -2053,133 +2058,133 @@
       <c r="J2" s="40"/>
       <c r="K2" s="40"/>
       <c r="L2" s="40"/>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="100" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="68"/>
-      <c r="AC2" s="106" t="s">
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
+      <c r="R2" s="100"/>
+      <c r="S2" s="100"/>
+      <c r="T2" s="100"/>
+      <c r="U2" s="100"/>
+      <c r="V2" s="100"/>
+      <c r="W2" s="100"/>
+      <c r="X2" s="100"/>
+      <c r="Y2" s="100"/>
+      <c r="Z2" s="100"/>
+      <c r="AA2" s="100"/>
+      <c r="AB2" s="101"/>
+      <c r="AC2" s="105" t="s">
         <v>95</v>
       </c>
-      <c r="AD2" s="107"/>
-      <c r="AE2" s="107"/>
-      <c r="AF2" s="108"/>
-      <c r="AG2" s="69" t="s">
+      <c r="AD2" s="106"/>
+      <c r="AE2" s="106"/>
+      <c r="AF2" s="107"/>
+      <c r="AG2" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="AH2" s="69"/>
-      <c r="AI2" s="69"/>
-      <c r="AJ2" s="69"/>
-      <c r="AK2" s="69"/>
-      <c r="AL2" s="60" t="s">
+      <c r="AH2" s="102"/>
+      <c r="AI2" s="102"/>
+      <c r="AJ2" s="102"/>
+      <c r="AK2" s="102"/>
+      <c r="AL2" s="110" t="s">
         <v>93</v>
       </c>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
-      <c r="AR2" s="61"/>
-      <c r="AS2" s="61"/>
-      <c r="AT2" s="61"/>
-      <c r="AU2" s="61"/>
-      <c r="AV2" s="61"/>
-      <c r="AW2" s="61"/>
-      <c r="AX2" s="62"/>
+      <c r="AM2" s="100"/>
+      <c r="AN2" s="100"/>
+      <c r="AO2" s="100"/>
+      <c r="AP2" s="100"/>
+      <c r="AQ2" s="100"/>
+      <c r="AR2" s="100"/>
+      <c r="AS2" s="100"/>
+      <c r="AT2" s="100"/>
+      <c r="AU2" s="100"/>
+      <c r="AV2" s="100"/>
+      <c r="AW2" s="100"/>
+      <c r="AX2" s="111"/>
     </row>
     <row r="3" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="45"/>
-      <c r="C3" s="89" t="s">
+      <c r="C3" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64" t="s">
+      <c r="D3" s="88"/>
+      <c r="E3" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64" t="s">
+      <c r="F3" s="88"/>
+      <c r="G3" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64" t="s">
+      <c r="H3" s="88"/>
+      <c r="I3" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64" t="s">
+      <c r="J3" s="88"/>
+      <c r="K3" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64" t="s">
+      <c r="L3" s="88"/>
+      <c r="M3" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64" t="s">
+      <c r="N3" s="88"/>
+      <c r="O3" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64" t="s">
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64" t="s">
+      <c r="R3" s="88"/>
+      <c r="S3" s="88" t="s">
         <v>94</v>
       </c>
-      <c r="T3" s="84"/>
-      <c r="U3" s="64" t="s">
+      <c r="T3" s="89"/>
+      <c r="U3" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="V3" s="64"/>
-      <c r="W3" s="64" t="s">
+      <c r="V3" s="88"/>
+      <c r="W3" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="X3" s="64"/>
-      <c r="Y3" s="64" t="s">
+      <c r="X3" s="88"/>
+      <c r="Y3" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="Z3" s="64"/>
-      <c r="AA3" s="64" t="s">
+      <c r="Z3" s="88"/>
+      <c r="AA3" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="AB3" s="84"/>
-      <c r="AC3" s="64" t="s">
+      <c r="AB3" s="89"/>
+      <c r="AC3" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="AD3" s="64"/>
-      <c r="AE3" s="64" t="s">
+      <c r="AD3" s="88"/>
+      <c r="AE3" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="AF3" s="64"/>
-      <c r="AG3" s="70"/>
-      <c r="AH3" s="70"/>
-      <c r="AI3" s="70"/>
-      <c r="AJ3" s="70"/>
-      <c r="AK3" s="70"/>
-      <c r="AL3" s="63"/>
-      <c r="AM3" s="64"/>
-      <c r="AN3" s="64"/>
-      <c r="AO3" s="64"/>
-      <c r="AP3" s="64"/>
-      <c r="AQ3" s="64"/>
-      <c r="AR3" s="64"/>
-      <c r="AS3" s="64"/>
-      <c r="AT3" s="64"/>
-      <c r="AU3" s="64"/>
-      <c r="AV3" s="64"/>
-      <c r="AW3" s="64"/>
-      <c r="AX3" s="65"/>
+      <c r="AF3" s="88"/>
+      <c r="AG3" s="103"/>
+      <c r="AH3" s="103"/>
+      <c r="AI3" s="103"/>
+      <c r="AJ3" s="103"/>
+      <c r="AK3" s="103"/>
+      <c r="AL3" s="112"/>
+      <c r="AM3" s="88"/>
+      <c r="AN3" s="88"/>
+      <c r="AO3" s="88"/>
+      <c r="AP3" s="88"/>
+      <c r="AQ3" s="88"/>
+      <c r="AR3" s="88"/>
+      <c r="AS3" s="88"/>
+      <c r="AT3" s="88"/>
+      <c r="AU3" s="88"/>
+      <c r="AV3" s="88"/>
+      <c r="AW3" s="88"/>
+      <c r="AX3" s="113"/>
     </row>
     <row r="4" spans="2:50" s="1" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="46"/>
@@ -2297,18 +2302,18 @@
       <c r="AN4" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="AO4" s="66" t="s">
+      <c r="AO4" s="104" t="s">
         <v>57</v>
       </c>
-      <c r="AP4" s="66"/>
-      <c r="AQ4" s="66" t="s">
+      <c r="AP4" s="104"/>
+      <c r="AQ4" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="AR4" s="66"/>
-      <c r="AS4" s="59" t="s">
+      <c r="AR4" s="104"/>
+      <c r="AS4" s="109" t="s">
         <v>59</v>
       </c>
-      <c r="AT4" s="59"/>
+      <c r="AT4" s="109"/>
       <c r="AU4" s="50" t="s">
         <v>60</v>
       </c>
@@ -2324,122 +2329,122 @@
       <c r="B5" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="90">
+      <c r="C5" s="58">
         <v>2681</v>
       </c>
-      <c r="D5" s="91">
+      <c r="D5" s="59">
         <v>3325</v>
       </c>
-      <c r="E5" s="91">
+      <c r="E5" s="59">
         <v>539</v>
       </c>
-      <c r="F5" s="91">
+      <c r="F5" s="59">
         <v>657</v>
       </c>
-      <c r="G5" s="91">
-        <v>0</v>
-      </c>
-      <c r="H5" s="91">
+      <c r="G5" s="59">
+        <v>0</v>
+      </c>
+      <c r="H5" s="59">
         <v>13</v>
       </c>
-      <c r="I5" s="91">
+      <c r="I5" s="59">
         <v>14</v>
       </c>
-      <c r="J5" s="91">
-        <v>0</v>
-      </c>
-      <c r="K5" s="91">
+      <c r="J5" s="59">
+        <v>0</v>
+      </c>
+      <c r="K5" s="59">
         <v>333</v>
       </c>
-      <c r="L5" s="91">
+      <c r="L5" s="59">
         <v>441</v>
       </c>
-      <c r="M5" s="91">
+      <c r="M5" s="59">
         <v>41000</v>
       </c>
-      <c r="N5" s="92">
+      <c r="N5" s="60">
         <v>36000</v>
       </c>
-      <c r="O5" s="92">
+      <c r="O5" s="60">
         <v>47000</v>
       </c>
-      <c r="P5" s="92">
+      <c r="P5" s="60">
         <v>42000</v>
       </c>
-      <c r="Q5" s="91">
+      <c r="Q5" s="59">
         <v>2400</v>
       </c>
-      <c r="R5" s="91">
+      <c r="R5" s="59">
         <v>2100</v>
       </c>
-      <c r="S5" s="91">
+      <c r="S5" s="59">
         <v>2500</v>
       </c>
-      <c r="T5" s="93">
+      <c r="T5" s="61">
         <v>2200</v>
       </c>
-      <c r="U5" s="92">
+      <c r="U5" s="60">
         <v>47000</v>
       </c>
-      <c r="V5" s="92">
+      <c r="V5" s="60">
         <v>42000</v>
       </c>
-      <c r="W5" s="92">
+      <c r="W5" s="60">
         <v>42000</v>
       </c>
-      <c r="X5" s="92">
+      <c r="X5" s="60">
         <v>37000</v>
       </c>
-      <c r="Y5" s="91">
+      <c r="Y5" s="59">
         <v>2900</v>
       </c>
-      <c r="Z5" s="91">
+      <c r="Z5" s="59">
         <v>2500</v>
       </c>
-      <c r="AA5" s="91">
+      <c r="AA5" s="59">
         <v>2500</v>
       </c>
-      <c r="AB5" s="93">
+      <c r="AB5" s="61">
         <v>2200</v>
       </c>
-      <c r="AC5" s="109">
+      <c r="AC5" s="74">
         <f>M5/R5</f>
         <v>19.523809523809526</v>
       </c>
-      <c r="AD5" s="110">
+      <c r="AD5" s="75">
         <f>N5/Q5</f>
         <v>15</v>
       </c>
-      <c r="AE5" s="110">
+      <c r="AE5" s="75">
         <f>O5/T5</f>
         <v>21.363636363636363</v>
       </c>
-      <c r="AF5" s="113">
+      <c r="AF5" s="78">
         <f>P5/U5</f>
         <v>0.8936170212765957</v>
       </c>
-      <c r="AG5" s="96">
+      <c r="AG5" s="64">
         <v>11000</v>
       </c>
-      <c r="AH5" s="94">
+      <c r="AH5" s="62">
         <v>5500</v>
       </c>
-      <c r="AI5" s="94">
+      <c r="AI5" s="62">
         <v>2000</v>
       </c>
-      <c r="AJ5" s="94">
+      <c r="AJ5" s="62">
         <v>61638</v>
       </c>
-      <c r="AK5" s="95">
+      <c r="AK5" s="63">
         <v>80138</v>
       </c>
       <c r="AL5" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="AM5" s="66" t="s">
+      <c r="AM5" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="AN5" s="66"/>
+      <c r="AN5" s="104"/>
       <c r="AO5" s="50" t="s">
         <v>65</v>
       </c>
@@ -2452,11 +2457,11 @@
       <c r="AR5" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="AS5" s="67" t="s">
+      <c r="AS5" s="114" t="s">
         <v>67</v>
       </c>
-      <c r="AT5" s="67"/>
-      <c r="AU5" s="67"/>
+      <c r="AT5" s="114"/>
+      <c r="AU5" s="114"/>
       <c r="AV5" s="50" t="s">
         <v>68</v>
       </c>
@@ -2469,135 +2474,135 @@
       <c r="B6" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="96">
+      <c r="C6" s="64">
         <v>2360</v>
       </c>
-      <c r="D6" s="94">
+      <c r="D6" s="62">
         <v>2649</v>
       </c>
-      <c r="E6" s="94">
+      <c r="E6" s="62">
         <v>484</v>
       </c>
-      <c r="F6" s="94">
+      <c r="F6" s="62">
         <v>311</v>
       </c>
-      <c r="G6" s="94">
-        <v>0</v>
-      </c>
-      <c r="H6" s="94">
+      <c r="G6" s="62">
+        <v>0</v>
+      </c>
+      <c r="H6" s="62">
         <v>5</v>
       </c>
-      <c r="I6" s="94">
+      <c r="I6" s="62">
         <v>15</v>
       </c>
-      <c r="J6" s="94">
+      <c r="J6" s="62">
         <v>27</v>
       </c>
-      <c r="K6" s="94">
+      <c r="K6" s="62">
         <v>338</v>
       </c>
-      <c r="L6" s="94">
+      <c r="L6" s="62">
         <v>381</v>
       </c>
-      <c r="M6" s="94">
+      <c r="M6" s="62">
         <v>29000</v>
       </c>
-      <c r="N6" s="97">
+      <c r="N6" s="65">
         <v>25000</v>
       </c>
-      <c r="O6" s="97">
+      <c r="O6" s="65">
         <v>30000</v>
       </c>
-      <c r="P6" s="97">
+      <c r="P6" s="65">
         <v>27000</v>
       </c>
-      <c r="Q6" s="94">
+      <c r="Q6" s="62">
         <v>1900</v>
       </c>
-      <c r="R6" s="94">
+      <c r="R6" s="62">
         <v>1700</v>
       </c>
-      <c r="S6" s="94">
+      <c r="S6" s="62">
         <v>2000</v>
       </c>
-      <c r="T6" s="98">
+      <c r="T6" s="66">
         <v>1700</v>
       </c>
-      <c r="U6" s="97">
+      <c r="U6" s="65">
         <v>30000</v>
       </c>
-      <c r="V6" s="97">
+      <c r="V6" s="65">
         <v>27000</v>
       </c>
-      <c r="W6" s="97">
+      <c r="W6" s="65">
         <v>25000</v>
       </c>
-      <c r="X6" s="97">
+      <c r="X6" s="65">
         <v>28000</v>
       </c>
-      <c r="Y6" s="94">
+      <c r="Y6" s="62">
         <v>2300</v>
       </c>
-      <c r="Z6" s="94">
+      <c r="Z6" s="62">
         <v>2000</v>
       </c>
-      <c r="AA6" s="94">
+      <c r="AA6" s="62">
         <v>2000</v>
       </c>
-      <c r="AB6" s="98">
+      <c r="AB6" s="66">
         <v>1700</v>
       </c>
-      <c r="AC6" s="109">
+      <c r="AC6" s="74">
         <f t="shared" ref="AC6:AC9" si="0">M6/R6</f>
         <v>17.058823529411764</v>
       </c>
-      <c r="AD6" s="110">
+      <c r="AD6" s="75">
         <f t="shared" ref="AD6:AD9" si="1">N6/Q6</f>
         <v>13.157894736842104</v>
       </c>
-      <c r="AE6" s="110">
+      <c r="AE6" s="75">
         <f t="shared" ref="AE6:AE9" si="2">O6/T6</f>
         <v>17.647058823529413</v>
       </c>
-      <c r="AF6" s="113">
+      <c r="AF6" s="78">
         <f t="shared" ref="AF6:AF9" si="3">P6/U6</f>
         <v>0.9</v>
       </c>
-      <c r="AG6" s="96">
+      <c r="AG6" s="64">
         <v>5500</v>
       </c>
-      <c r="AH6" s="94">
+      <c r="AH6" s="62">
         <v>2200</v>
       </c>
-      <c r="AI6" s="94">
+      <c r="AI6" s="62">
         <v>5000</v>
       </c>
-      <c r="AJ6" s="94">
+      <c r="AJ6" s="62">
         <v>70782</v>
       </c>
-      <c r="AK6" s="95">
+      <c r="AK6" s="63">
         <v>83482</v>
       </c>
       <c r="AL6" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="AM6" s="66" t="s">
+      <c r="AM6" s="104" t="s">
         <v>71</v>
       </c>
-      <c r="AN6" s="66"/>
-      <c r="AO6" s="67" t="s">
+      <c r="AN6" s="104"/>
+      <c r="AO6" s="114" t="s">
         <v>65</v>
       </c>
-      <c r="AP6" s="67"/>
-      <c r="AQ6" s="67" t="s">
+      <c r="AP6" s="114"/>
+      <c r="AQ6" s="114" t="s">
         <v>65</v>
       </c>
-      <c r="AR6" s="67"/>
-      <c r="AS6" s="67" t="s">
+      <c r="AR6" s="114"/>
+      <c r="AS6" s="114" t="s">
         <v>67</v>
       </c>
-      <c r="AT6" s="67"/>
-      <c r="AU6" s="67"/>
+      <c r="AT6" s="114"/>
+      <c r="AU6" s="114"/>
       <c r="AV6" s="50" t="s">
         <v>68</v>
       </c>
@@ -2610,137 +2615,137 @@
       <c r="B7" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="96">
+      <c r="C7" s="64">
         <v>2805</v>
       </c>
-      <c r="D7" s="94">
+      <c r="D7" s="62">
         <v>2562</v>
       </c>
-      <c r="E7" s="94">
+      <c r="E7" s="62">
         <v>143</v>
       </c>
-      <c r="F7" s="94">
+      <c r="F7" s="62">
         <v>126</v>
       </c>
-      <c r="G7" s="94">
+      <c r="G7" s="62">
         <v>343</v>
       </c>
-      <c r="H7" s="94">
+      <c r="H7" s="62">
         <v>369</v>
       </c>
-      <c r="I7" s="99">
-        <v>0</v>
-      </c>
-      <c r="J7" s="99">
-        <v>0</v>
-      </c>
-      <c r="K7" s="94">
+      <c r="I7" s="67">
+        <v>0</v>
+      </c>
+      <c r="J7" s="67">
+        <v>0</v>
+      </c>
+      <c r="K7" s="62">
         <v>244</v>
       </c>
-      <c r="L7" s="94">
+      <c r="L7" s="62">
         <v>187</v>
       </c>
-      <c r="M7" s="94">
+      <c r="M7" s="62">
         <v>20000</v>
       </c>
-      <c r="N7" s="97">
+      <c r="N7" s="65">
         <v>18000</v>
       </c>
-      <c r="O7" s="97">
+      <c r="O7" s="65">
         <v>22000</v>
       </c>
-      <c r="P7" s="97">
+      <c r="P7" s="65">
         <v>20000</v>
       </c>
-      <c r="Q7" s="94">
+      <c r="Q7" s="62">
         <v>660</v>
       </c>
-      <c r="R7" s="94">
+      <c r="R7" s="62">
         <v>600</v>
       </c>
-      <c r="S7" s="94">
+      <c r="S7" s="62">
         <v>750</v>
       </c>
-      <c r="T7" s="98">
+      <c r="T7" s="66">
         <v>670</v>
       </c>
-      <c r="U7" s="97">
+      <c r="U7" s="65">
         <v>22000</v>
       </c>
-      <c r="V7" s="97">
+      <c r="V7" s="65">
         <v>20000</v>
       </c>
-      <c r="W7" s="97">
+      <c r="W7" s="65">
         <v>20000</v>
       </c>
-      <c r="X7" s="97">
+      <c r="X7" s="65">
         <v>18000</v>
       </c>
-      <c r="Y7" s="94">
+      <c r="Y7" s="62">
         <v>920</v>
       </c>
-      <c r="Z7" s="94">
+      <c r="Z7" s="62">
         <v>820</v>
       </c>
-      <c r="AA7" s="94">
+      <c r="AA7" s="62">
         <v>750</v>
       </c>
-      <c r="AB7" s="98">
+      <c r="AB7" s="66">
         <v>670</v>
       </c>
-      <c r="AC7" s="109">
+      <c r="AC7" s="74">
         <f t="shared" si="0"/>
         <v>33.333333333333336</v>
       </c>
-      <c r="AD7" s="110">
+      <c r="AD7" s="75">
         <f t="shared" si="1"/>
         <v>27.272727272727273</v>
       </c>
-      <c r="AE7" s="110">
+      <c r="AE7" s="75">
         <f t="shared" si="2"/>
         <v>32.835820895522389</v>
       </c>
-      <c r="AF7" s="113">
+      <c r="AF7" s="78">
         <f t="shared" si="3"/>
         <v>0.90909090909090906</v>
       </c>
-      <c r="AG7" s="96">
+      <c r="AG7" s="64">
         <v>9900</v>
       </c>
-      <c r="AH7" s="94">
+      <c r="AH7" s="62">
         <v>3300</v>
       </c>
-      <c r="AI7" s="94">
+      <c r="AI7" s="62">
         <v>5000</v>
       </c>
-      <c r="AJ7" s="94">
+      <c r="AJ7" s="62">
         <v>114120</v>
       </c>
-      <c r="AK7" s="95">
+      <c r="AK7" s="63">
         <v>132320</v>
       </c>
       <c r="AL7" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="AM7" s="66" t="s">
+      <c r="AM7" s="104" t="s">
         <v>74</v>
       </c>
-      <c r="AN7" s="66"/>
+      <c r="AN7" s="104"/>
       <c r="AO7" s="50" t="s">
         <v>75</v>
       </c>
       <c r="AP7" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="AQ7" s="67" t="s">
+      <c r="AQ7" s="114" t="s">
         <v>77</v>
       </c>
-      <c r="AR7" s="67"/>
-      <c r="AS7" s="67" t="s">
+      <c r="AR7" s="114"/>
+      <c r="AS7" s="114" t="s">
         <v>67</v>
       </c>
-      <c r="AT7" s="67"/>
-      <c r="AU7" s="67"/>
+      <c r="AT7" s="114"/>
+      <c r="AU7" s="114"/>
       <c r="AV7" s="50" t="s">
         <v>68</v>
       </c>
@@ -2753,113 +2758,113 @@
       <c r="B8" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="96">
+      <c r="C8" s="64">
         <v>1449</v>
       </c>
-      <c r="D8" s="94">
+      <c r="D8" s="62">
         <v>1712</v>
       </c>
-      <c r="E8" s="94">
+      <c r="E8" s="62">
         <v>241</v>
       </c>
-      <c r="F8" s="94">
+      <c r="F8" s="62">
         <v>286</v>
       </c>
-      <c r="G8" s="94">
+      <c r="G8" s="62">
         <v>20</v>
       </c>
-      <c r="H8" s="94">
+      <c r="H8" s="62">
         <v>23</v>
       </c>
-      <c r="I8" s="99">
-        <v>0</v>
-      </c>
-      <c r="J8" s="99">
-        <v>0</v>
-      </c>
-      <c r="K8" s="94">
+      <c r="I8" s="67">
+        <v>0</v>
+      </c>
+      <c r="J8" s="67">
+        <v>0</v>
+      </c>
+      <c r="K8" s="62">
         <v>108</v>
       </c>
-      <c r="L8" s="94">
+      <c r="L8" s="62">
         <v>149</v>
       </c>
-      <c r="M8" s="94">
+      <c r="M8" s="62">
         <v>34000</v>
       </c>
-      <c r="N8" s="97">
+      <c r="N8" s="65">
         <v>30000</v>
       </c>
-      <c r="O8" s="97">
+      <c r="O8" s="65">
         <v>37000</v>
       </c>
-      <c r="P8" s="97">
+      <c r="P8" s="65">
         <v>33000</v>
       </c>
-      <c r="Q8" s="94">
+      <c r="Q8" s="62">
         <v>2200</v>
       </c>
-      <c r="R8" s="94">
+      <c r="R8" s="62">
         <v>1900</v>
       </c>
-      <c r="S8" s="94">
+      <c r="S8" s="62">
         <v>2200</v>
       </c>
-      <c r="T8" s="98">
+      <c r="T8" s="66">
         <v>2000</v>
       </c>
-      <c r="U8" s="97">
+      <c r="U8" s="65">
         <v>37000</v>
       </c>
-      <c r="V8" s="97">
+      <c r="V8" s="65">
         <v>33000</v>
       </c>
-      <c r="W8" s="97">
+      <c r="W8" s="65">
         <v>32000</v>
       </c>
-      <c r="X8" s="97">
+      <c r="X8" s="65">
         <v>29000</v>
       </c>
-      <c r="Y8" s="94">
+      <c r="Y8" s="62">
         <v>2900</v>
       </c>
-      <c r="Z8" s="94">
+      <c r="Z8" s="62">
         <v>2600</v>
       </c>
-      <c r="AA8" s="94">
+      <c r="AA8" s="62">
         <v>2200</v>
       </c>
-      <c r="AB8" s="98">
+      <c r="AB8" s="66">
         <v>2000</v>
       </c>
-      <c r="AC8" s="109">
+      <c r="AC8" s="74">
         <f t="shared" si="0"/>
         <v>17.894736842105264</v>
       </c>
-      <c r="AD8" s="110">
+      <c r="AD8" s="75">
         <f t="shared" si="1"/>
         <v>13.636363636363637</v>
       </c>
-      <c r="AE8" s="110">
+      <c r="AE8" s="75">
         <f t="shared" si="2"/>
         <v>18.5</v>
       </c>
-      <c r="AF8" s="113">
+      <c r="AF8" s="78">
         <f t="shared" si="3"/>
         <v>0.89189189189189189</v>
       </c>
-      <c r="AG8" s="96">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="94">
+      <c r="AG8" s="64">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="62">
         <v>3300</v>
       </c>
-      <c r="AI8" s="94">
+      <c r="AI8" s="62">
         <v>1500</v>
       </c>
-      <c r="AJ8" s="94">
+      <c r="AJ8" s="62">
         <v>68272</v>
       </c>
-      <c r="AK8" s="95">
+      <c r="AK8" s="63">
         <v>73072</v>
       </c>
       <c r="AL8" s="53" t="s">
@@ -2871,19 +2876,19 @@
       <c r="AN8" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="AO8" s="67" t="s">
+      <c r="AO8" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="AP8" s="67"/>
-      <c r="AQ8" s="67" t="s">
+      <c r="AP8" s="114"/>
+      <c r="AQ8" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="AR8" s="67"/>
-      <c r="AS8" s="67" t="s">
+      <c r="AR8" s="114"/>
+      <c r="AS8" s="114" t="s">
         <v>67</v>
       </c>
-      <c r="AT8" s="67"/>
-      <c r="AU8" s="67"/>
+      <c r="AT8" s="114"/>
+      <c r="AU8" s="114"/>
       <c r="AV8" s="50" t="s">
         <v>68</v>
       </c>
@@ -2896,122 +2901,122 @@
       <c r="B9" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="100">
+      <c r="C9" s="68">
         <v>1484</v>
       </c>
-      <c r="D9" s="101">
+      <c r="D9" s="69">
         <v>1510</v>
       </c>
-      <c r="E9" s="101">
+      <c r="E9" s="69">
         <v>125</v>
       </c>
-      <c r="F9" s="101">
+      <c r="F9" s="69">
         <v>81</v>
       </c>
-      <c r="G9" s="101">
+      <c r="G9" s="69">
         <v>53</v>
       </c>
-      <c r="H9" s="101">
+      <c r="H9" s="69">
         <v>55</v>
       </c>
-      <c r="I9" s="102">
-        <v>0</v>
-      </c>
-      <c r="J9" s="102">
-        <v>0</v>
-      </c>
-      <c r="K9" s="101">
+      <c r="I9" s="70">
+        <v>0</v>
+      </c>
+      <c r="J9" s="70">
+        <v>0</v>
+      </c>
+      <c r="K9" s="69">
         <v>132</v>
       </c>
-      <c r="L9" s="101">
+      <c r="L9" s="69">
         <v>129</v>
       </c>
-      <c r="M9" s="101">
+      <c r="M9" s="69">
         <v>60000</v>
       </c>
-      <c r="N9" s="103">
+      <c r="N9" s="71">
         <v>54000</v>
       </c>
-      <c r="O9" s="103">
+      <c r="O9" s="71">
         <v>72000</v>
       </c>
-      <c r="P9" s="103">
+      <c r="P9" s="71">
         <v>65000</v>
       </c>
-      <c r="Q9" s="101">
+      <c r="Q9" s="69">
         <v>1100</v>
       </c>
-      <c r="R9" s="101">
+      <c r="R9" s="69">
         <v>900</v>
       </c>
-      <c r="S9" s="101">
+      <c r="S9" s="69">
         <v>1100</v>
       </c>
-      <c r="T9" s="104">
+      <c r="T9" s="72">
         <v>900</v>
       </c>
-      <c r="U9" s="103">
+      <c r="U9" s="71">
         <v>72000</v>
       </c>
-      <c r="V9" s="103">
+      <c r="V9" s="71">
         <v>65000</v>
       </c>
-      <c r="W9" s="103">
+      <c r="W9" s="71">
         <v>72000</v>
       </c>
-      <c r="X9" s="103">
+      <c r="X9" s="71">
         <v>65000</v>
       </c>
-      <c r="Y9" s="101">
+      <c r="Y9" s="69">
         <v>1500</v>
       </c>
-      <c r="Z9" s="101">
+      <c r="Z9" s="69">
         <v>1300</v>
       </c>
-      <c r="AA9" s="101">
+      <c r="AA9" s="69">
         <v>1100</v>
       </c>
-      <c r="AB9" s="104">
+      <c r="AB9" s="72">
         <v>900</v>
       </c>
-      <c r="AC9" s="111">
+      <c r="AC9" s="76">
         <f t="shared" si="0"/>
         <v>66.666666666666671</v>
       </c>
-      <c r="AD9" s="112">
+      <c r="AD9" s="77">
         <f t="shared" si="1"/>
         <v>49.090909090909093</v>
       </c>
-      <c r="AE9" s="112">
+      <c r="AE9" s="77">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="AF9" s="114">
+      <c r="AF9" s="79">
         <f t="shared" si="3"/>
         <v>0.90277777777777779</v>
       </c>
-      <c r="AG9" s="100">
+      <c r="AG9" s="68">
         <v>25000</v>
       </c>
-      <c r="AH9" s="101">
+      <c r="AH9" s="69">
         <v>1500</v>
       </c>
-      <c r="AI9" s="101">
+      <c r="AI9" s="69">
         <v>10000</v>
       </c>
-      <c r="AJ9" s="101">
+      <c r="AJ9" s="69">
         <v>273300</v>
       </c>
-      <c r="AK9" s="105">
+      <c r="AK9" s="73">
         <v>309800</v>
       </c>
       <c r="AL9" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="AM9" s="58" t="s">
+      <c r="AM9" s="108" t="s">
         <v>84</v>
       </c>
-      <c r="AN9" s="58"/>
+      <c r="AN9" s="108"/>
       <c r="AO9" s="55" t="s">
         <v>82</v>
       </c>
@@ -3062,109 +3067,109 @@
     </row>
     <row r="18" spans="2:35" s="7" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="8"/>
-      <c r="C18" s="85" t="s">
+      <c r="C18" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="86"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="86"/>
-      <c r="G18" s="86"/>
-      <c r="H18" s="86"/>
-      <c r="I18" s="86"/>
-      <c r="J18" s="86"/>
-      <c r="K18" s="87"/>
-      <c r="L18" s="88" t="s">
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="81"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="81"/>
+      <c r="K18" s="82"/>
+      <c r="L18" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="M18" s="86"/>
-      <c r="N18" s="86"/>
-      <c r="O18" s="86"/>
-      <c r="P18" s="86"/>
-      <c r="Q18" s="87"/>
-      <c r="R18" s="78" t="s">
+      <c r="M18" s="81"/>
+      <c r="N18" s="81"/>
+      <c r="O18" s="81"/>
+      <c r="P18" s="81"/>
+      <c r="Q18" s="82"/>
+      <c r="R18" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="S18" s="76"/>
-      <c r="T18" s="76"/>
-      <c r="U18" s="76"/>
-      <c r="V18" s="76"/>
-      <c r="W18" s="77"/>
-      <c r="X18" s="75" t="s">
+      <c r="S18" s="85"/>
+      <c r="T18" s="85"/>
+      <c r="U18" s="85"/>
+      <c r="V18" s="85"/>
+      <c r="W18" s="86"/>
+      <c r="X18" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="Y18" s="76"/>
-      <c r="Z18" s="76"/>
-      <c r="AA18" s="76"/>
-      <c r="AB18" s="76"/>
-      <c r="AC18" s="77"/>
-      <c r="AD18" s="78" t="s">
+      <c r="Y18" s="85"/>
+      <c r="Z18" s="85"/>
+      <c r="AA18" s="85"/>
+      <c r="AB18" s="85"/>
+      <c r="AC18" s="86"/>
+      <c r="AD18" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="AE18" s="76"/>
-      <c r="AF18" s="76"/>
-      <c r="AG18" s="76"/>
-      <c r="AH18" s="76"/>
-      <c r="AI18" s="77"/>
+      <c r="AE18" s="85"/>
+      <c r="AF18" s="85"/>
+      <c r="AG18" s="85"/>
+      <c r="AH18" s="85"/>
+      <c r="AI18" s="86"/>
     </row>
     <row r="19" spans="2:35" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B19" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="79">
+      <c r="C19" s="94">
         <v>2023</v>
       </c>
-      <c r="D19" s="80"/>
-      <c r="E19" s="81"/>
-      <c r="F19" s="82">
+      <c r="D19" s="95"/>
+      <c r="E19" s="96"/>
+      <c r="F19" s="97">
         <v>2024</v>
       </c>
-      <c r="G19" s="80"/>
-      <c r="H19" s="83"/>
-      <c r="I19" s="79">
-        <v>2025</v>
-      </c>
-      <c r="J19" s="80"/>
-      <c r="K19" s="83"/>
-      <c r="L19" s="71">
+      <c r="G19" s="95"/>
+      <c r="H19" s="98"/>
+      <c r="I19" s="94">
+        <v>2025</v>
+      </c>
+      <c r="J19" s="95"/>
+      <c r="K19" s="98"/>
+      <c r="L19" s="90">
         <v>2023</v>
       </c>
-      <c r="M19" s="72"/>
-      <c r="N19" s="74"/>
-      <c r="O19" s="79">
+      <c r="M19" s="91"/>
+      <c r="N19" s="92"/>
+      <c r="O19" s="94">
         <v>2024</v>
       </c>
-      <c r="P19" s="80"/>
-      <c r="Q19" s="81"/>
-      <c r="R19" s="71">
+      <c r="P19" s="95"/>
+      <c r="Q19" s="96"/>
+      <c r="R19" s="90">
         <v>2023</v>
       </c>
-      <c r="S19" s="72"/>
-      <c r="T19" s="74"/>
-      <c r="U19" s="71">
+      <c r="S19" s="91"/>
+      <c r="T19" s="92"/>
+      <c r="U19" s="90">
         <v>2024</v>
       </c>
-      <c r="V19" s="72"/>
-      <c r="W19" s="73"/>
-      <c r="X19" s="71">
+      <c r="V19" s="91"/>
+      <c r="W19" s="93"/>
+      <c r="X19" s="90">
         <v>2023</v>
       </c>
-      <c r="Y19" s="72"/>
-      <c r="Z19" s="74"/>
-      <c r="AA19" s="71">
+      <c r="Y19" s="91"/>
+      <c r="Z19" s="92"/>
+      <c r="AA19" s="90">
         <v>2024</v>
       </c>
-      <c r="AB19" s="72"/>
-      <c r="AC19" s="73"/>
-      <c r="AD19" s="71">
+      <c r="AB19" s="91"/>
+      <c r="AC19" s="93"/>
+      <c r="AD19" s="90">
         <v>2023</v>
       </c>
-      <c r="AE19" s="72"/>
-      <c r="AF19" s="74"/>
-      <c r="AG19" s="71">
+      <c r="AE19" s="91"/>
+      <c r="AF19" s="92"/>
+      <c r="AG19" s="90">
         <v>2024</v>
       </c>
-      <c r="AH19" s="72"/>
-      <c r="AI19" s="74"/>
+      <c r="AH19" s="91"/>
+      <c r="AI19" s="92"/>
     </row>
     <row r="20" spans="2:35" s="7" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="11" t="s">
@@ -6970,43 +6975,6 @@
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="C18:K18"/>
-    <mergeCell ref="L18:Q18"/>
-    <mergeCell ref="R18:W18"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="R19:T19"/>
-    <mergeCell ref="U19:W19"/>
-    <mergeCell ref="X19:Z19"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="W3:X3"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="AA19:AC19"/>
-    <mergeCell ref="AD19:AF19"/>
-    <mergeCell ref="AG19:AI19"/>
-    <mergeCell ref="X18:AC18"/>
-    <mergeCell ref="AD18:AI18"/>
-    <mergeCell ref="M2:AB2"/>
-    <mergeCell ref="AG2:AK3"/>
-    <mergeCell ref="AO4:AP4"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="AM5:AN5"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="AC2:AF2"/>
     <mergeCell ref="AM9:AN9"/>
     <mergeCell ref="AS4:AT4"/>
     <mergeCell ref="AL2:AX3"/>
@@ -7021,6 +6989,43 @@
     <mergeCell ref="AO6:AP6"/>
     <mergeCell ref="AQ6:AR6"/>
     <mergeCell ref="AS6:AU6"/>
+    <mergeCell ref="AO4:AP4"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="AM5:AN5"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AD19:AF19"/>
+    <mergeCell ref="AG19:AI19"/>
+    <mergeCell ref="X18:AC18"/>
+    <mergeCell ref="AD18:AI18"/>
+    <mergeCell ref="M2:AB2"/>
+    <mergeCell ref="AG2:AK3"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="AA19:AC19"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="U19:W19"/>
+    <mergeCell ref="X19:Z19"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="C18:K18"/>
+    <mergeCell ref="L18:Q18"/>
+    <mergeCell ref="R18:W18"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="S3:T3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
